--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S6_IAM_Compliance_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S6_IAM_Compliance_Dashboard_20260208.xlsx
@@ -170,7 +170,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <row r="6" ht="35" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>+6%</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1167,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Access Review Results (86%)</t>
+          <t>Access Review Results (92%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Access Rights Matrix (83%)</t>
+          <t>User Inventory &amp; Lifecycle (91%)</t>
         </is>
       </c>
     </row>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Role Definition &amp; SoD (72%)</t>
+          <t>Access Rights Matrix (78%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>User Inventory &amp; Lifecycle (81%)</t>
+          <t>Role Definition &amp; SoD (82%)</t>
         </is>
       </c>
     </row>
@@ -1265,9 +1265,9 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Mostly Ready</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Declining</t>
+          <t>+6%</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1456,9 +1456,9 @@
           <t>Warning</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Stable</t>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1503,9 +1503,9 @@
           <t>Compliant</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Improving</t>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1550,9 +1550,9 @@
           <t>Warning</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Declining</t>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Declining</t>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Total Gaps: 25 | Critical: 1 | High: 6 | Open: 11</t>
+          <t>Total Gaps: 25 | Critical: 3 | High: 7 | Open: 11</t>
         </is>
       </c>
     </row>
@@ -1730,22 +1730,22 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GAP-005</t>
+          <t>GAP-002</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation</t>
+          <t>RBAC Adoption</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation gap requiring attention</t>
+          <t>RBAC Adoption gap requiring attention</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1754,31 +1754,31 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access documentation procedures</t>
+          <t>Process gap in rbac adoption procedures</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access documentation controls</t>
+          <t>Implement automated rbac adoption controls</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Security Team</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>29.03.2026</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="L6" s="6" t="n"/>
@@ -1786,7 +1786,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GAP-002</t>
+          <t>GAP-010</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1804,13 +1804,13 @@
           <t>Leaver SLA gap requiring attention</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1824,17 +1824,17 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L7" s="6" t="n"/>
@@ -1842,40 +1842,40 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>GAP-004</t>
+          <t>GAP-012</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>RBAC Adoption</t>
+          <t>Contractor Expiry</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>RBAC Adoption gap requiring attention</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Contractor Expiry gap requiring attention</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Process gap in rbac adoption procedures</t>
+          <t>Process gap in contractor expiry procedures</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Implement automated rbac adoption controls</t>
+          <t>Implement automated contractor expiry controls</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>03.03.2026</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>03.04.2026</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L8" s="6" t="n"/>
@@ -1898,22 +1898,22 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GAP-006</t>
+          <t>GAP-005</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Access Review</t>
+          <t>Contractor Expiry</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Access Review gap requiring attention</t>
+          <t>Contractor Expiry gap requiring attention</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access review procedures</t>
+          <t>Process gap in contractor expiry procedures</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access review controls</t>
+          <t>Implement automated contractor expiry controls</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>CISO</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>02.05.2026</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="L9" s="6" t="n"/>
@@ -1954,22 +1954,22 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GAP-009</t>
+          <t>GAP-008</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation gap requiring attention</t>
+          <t>Provisioning gap requiring attention</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1978,26 +1978,26 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access documentation procedures</t>
+          <t>Process gap in provisioning procedures</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access documentation controls</t>
+          <t>Implement automated provisioning controls</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IAM Manager</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>29.03.2026</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -2010,22 +2010,22 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GAP-017</t>
+          <t>GAP-009</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Attestation</t>
+          <t>Excessive Access</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Attestation gap requiring attention</t>
+          <t>Excessive Access gap requiring attention</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2034,26 +2034,26 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Process gap in attestation procedures</t>
+          <t>Process gap in excessive access procedures</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Implement automated attestation controls</t>
+          <t>Implement automated excessive access controls</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Security Team</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -2066,22 +2066,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GAP-019</t>
+          <t>GAP-014</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Privileged Access</t>
+          <t>Orphaned Accounts</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Privileged Access gap requiring attention</t>
+          <t>Orphaned Accounts gap requiring attention</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Process gap in privileged access procedures</t>
+          <t>Process gap in orphaned accounts procedures</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Implement automated privileged access controls</t>
+          <t>Implement automated orphaned accounts controls</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>11.03.2026</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -2122,55 +2122,55 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GAP-001</t>
+          <t>GAP-020</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry</t>
+          <t>Access Documentation</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry gap requiring attention</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Access Documentation gap requiring attention</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Process gap in contractor expiry procedures</t>
+          <t>Process gap in access documentation procedures</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Implement automated contractor expiry controls</t>
+          <t>Implement automated access documentation controls</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IAM Manager</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L13" s="6" t="n"/>
@@ -2178,55 +2178,55 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GAP-007</t>
+          <t>GAP-021</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation</t>
+          <t>Access Review</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Access Documentation gap requiring attention</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Access Review gap requiring attention</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access documentation procedures</t>
+          <t>Process gap in access review procedures</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access documentation controls</t>
+          <t>Implement automated access review controls</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IAM Manager</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>06.03.2026</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="L14" s="6" t="n"/>
@@ -2234,27 +2234,27 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GAP-008</t>
+          <t>GAP-023</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>RBAC Adoption</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>RBAC Adoption gap requiring attention</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Provisioning gap requiring attention</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -2262,27 +2262,27 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Process gap in rbac adoption procedures</t>
+          <t>Process gap in provisioning procedures</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Implement automated rbac adoption controls</t>
+          <t>Implement automated provisioning controls</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>28.03.2026</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L15" s="6" t="n"/>
@@ -2290,7 +2290,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GAP-010</t>
+          <t>GAP-001</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
@@ -2346,22 +2346,22 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>GAP-013</t>
+          <t>GAP-004</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry</t>
+          <t>Privileged Access</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry gap requiring attention</t>
+          <t>Privileged Access gap requiring attention</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2370,31 +2370,31 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Process gap in contractor expiry procedures</t>
+          <t>Process gap in privileged access procedures</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Implement automated contractor expiry controls</t>
+          <t>Implement automated privileged access controls</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>29.04.2026</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="L17" s="6" t="n"/>
@@ -2402,7 +2402,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GAP-014</t>
+          <t>GAP-006</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>14.04.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
@@ -2458,22 +2458,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GAP-015</t>
+          <t>GAP-011</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Privileged Access</t>
+          <t>Access Review</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Privileged Access gap requiring attention</t>
+          <t>Access Review gap requiring attention</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -2482,26 +2482,26 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Process gap in privileged access procedures</t>
+          <t>Process gap in access review procedures</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Implement automated privileged access controls</t>
+          <t>Implement automated access review controls</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>26.03.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
@@ -2514,22 +2514,22 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GAP-018</t>
+          <t>GAP-015</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Excessive Access</t>
+          <t>Deprovisioning</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Excessive Access gap requiring attention</t>
+          <t>Deprovisioning gap requiring attention</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2538,31 +2538,31 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Process gap in excessive access procedures</t>
+          <t>Process gap in deprovisioning procedures</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Implement automated excessive access controls</t>
+          <t>Implement automated deprovisioning controls</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L20" s="6" t="n"/>
@@ -2570,22 +2570,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>GAP-021</t>
+          <t>GAP-016</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Attestation</t>
+          <t>Deprovisioning</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Attestation gap requiring attention</t>
+          <t>Deprovisioning gap requiring attention</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -2594,31 +2594,31 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Process gap in attestation procedures</t>
+          <t>Process gap in deprovisioning procedures</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Implement automated attestation controls</t>
+          <t>Implement automated deprovisioning controls</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>29.04.2026</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L21" s="6" t="n"/>
@@ -2626,7 +2626,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GAP-024</t>
+          <t>GAP-019</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Orphaned Accounts</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Orphaned Accounts gap requiring attention</t>
+          <t>Provisioning gap requiring attention</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -2650,16 +2650,16 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Process gap in orphaned accounts procedures</t>
+          <t>Process gap in provisioning procedures</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Implement automated orphaned accounts controls</t>
+          <t>Implement automated provisioning controls</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>18.03.2026</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -2682,55 +2682,55 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>GAP-003</t>
+          <t>GAP-022</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Excessive Access</t>
+          <t>RBAC Adoption</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Excessive Access gap requiring attention</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>RBAC Adoption gap requiring attention</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Process gap in excessive access procedures</t>
+          <t>Process gap in rbac adoption procedures</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Implement automated excessive access controls</t>
+          <t>Implement automated rbac adoption controls</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>IAM Manager</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L23" s="6" t="n"/>
@@ -2738,22 +2738,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GAP-011</t>
+          <t>GAP-003</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry</t>
+          <t>SoD Violation</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Contractor Expiry gap requiring attention</t>
+          <t>SoD Violation gap requiring attention</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Process gap in contractor expiry procedures</t>
+          <t>Process gap in sod violation procedures</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Implement automated contractor expiry controls</t>
+          <t>Implement automated sod violation controls</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -2794,22 +2794,22 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>GAP-012</t>
+          <t>GAP-007</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Provisioning</t>
+          <t>Contractor Expiry</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Provisioning gap requiring attention</t>
+          <t>Contractor Expiry gap requiring attention</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2818,31 +2818,31 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Process gap in provisioning procedures</t>
+          <t>Process gap in contractor expiry procedures</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Implement automated provisioning controls</t>
+          <t>Implement automated contractor expiry controls</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>04.05.2026</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L25" s="6" t="n"/>
@@ -2850,22 +2850,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>GAP-016</t>
+          <t>GAP-013</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Attestation</t>
+          <t>Joiner SLA</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Attestation gap requiring attention</t>
+          <t>Joiner SLA gap requiring attention</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2874,31 +2874,31 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Process gap in attestation procedures</t>
+          <t>Process gap in joiner sla procedures</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Implement automated attestation controls</t>
+          <t>Implement automated joiner sla controls</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>IAM Manager</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>24.03.2026</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L26" s="6" t="n"/>
@@ -2906,22 +2906,22 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>GAP-020</t>
+          <t>GAP-017</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Access Review</t>
+          <t>Leaver SLA</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Access Review gap requiring attention</t>
+          <t>Leaver SLA gap requiring attention</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -2930,31 +2930,31 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access review procedures</t>
+          <t>Process gap in leaver sla procedures</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access review controls</t>
+          <t>Implement automated leaver sla controls</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>CISO</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="L27" s="6" t="n"/>
@@ -2962,22 +2962,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>GAP-022</t>
+          <t>GAP-018</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Attestation</t>
+          <t>Leaver SLA</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Attestation gap requiring attention</t>
+          <t>Leaver SLA gap requiring attention</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2986,31 +2986,31 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Process gap in attestation procedures</t>
+          <t>Process gap in leaver sla procedures</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Implement automated attestation controls</t>
+          <t>Implement automated leaver sla controls</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>01.05.2026</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L28" s="6" t="n"/>
@@ -3018,22 +3018,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GAP-023</t>
+          <t>GAP-024</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Access Review</t>
+          <t>RBAC Adoption</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Access Review gap requiring attention</t>
+          <t>RBAC Adoption gap requiring attention</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -3042,31 +3042,31 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access review procedures</t>
+          <t>Process gap in rbac adoption procedures</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access review controls</t>
+          <t>Implement automated rbac adoption controls</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t>04.04.2026</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="L29" s="6" t="n"/>
@@ -3079,17 +3079,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Access Review</t>
+          <t>Orphaned Accounts</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Access Review gap requiring attention</t>
+          <t>Orphaned Accounts gap requiring attention</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Process gap in access review procedures</t>
+          <t>Process gap in orphaned accounts procedures</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Implement automated access review controls</t>
+          <t>Implement automated orphaned accounts controls</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>09.03.2026</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>29.03.2026</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="L30" s="6" t="n"/>
@@ -3228,22 +3228,22 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>-1.0%</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Improving</t>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -3325,9 +3325,9 @@
           <t>Warning</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Stable</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -3367,9 +3367,9 @@
           <t>Warning</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Declining</t>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -3396,17 +3396,17 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>+5.0%</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -3522,22 +3522,22 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Declining</t>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -3577,9 +3577,9 @@
           <t>Warning</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Stable</t>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Improving</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>-2.0%</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>-15.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-2.0%</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>+10.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Total Evidence: 30 | Complete: 15 (50%) | Partial: 14 | Missing: 1</t>
+          <t>Total Evidence: 30 | Complete: 23 (77%) | Partial: 3 | Missing: 4</t>
         </is>
       </c>
     </row>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>A.5.18</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Lifecycle Metrics</t>
+          <t>SoD Matrix</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Process Records</t>
+          <t>Spreadsheet</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>S1 Assessment Workbook</t>
+          <t>S4 Assessment Workbook</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -3865,27 +3865,27 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>Attestation Records</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Approval Records</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S3 Assessment Workbook</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Group Memberships</t>
+          <t>SoD Matrix</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Export Data</t>
+          <t>Spreadsheet</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>S2 Assessment Workbook</t>
+          <t>S4 Assessment Workbook</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -3940,14 +3940,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Complete</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Audit Team</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -3964,17 +3964,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Procedure Guide</t>
+          <t>IAM Policy</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Process Document</t>
+          <t>Policy Document</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>A.5.18</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Audit Team</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -4081,14 +4081,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IAM Manager</t>
         </is>
       </c>
     </row>
@@ -4100,27 +4100,27 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Lifecycle Metrics</t>
+          <t>HR Integration</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Process Records</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>S1 Assessment Workbook</t>
+          <t>S5 Assessment Workbook</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -4128,14 +4128,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -4147,27 +4147,27 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.15</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>User Inventory</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Spreadsheet</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S1 Assessment Workbook</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>A.5.18</t>
+          <t>A.5.15</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Orphaned Scan</t>
+          <t>Procedure Guide</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Scan Results</t>
+          <t>Process Document</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>S1 Assessment Workbook</t>
+          <t>ISMS Evidence Library</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Access Matrix</t>
+          <t>Group Memberships</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Spreadsheet</t>
+          <t>Export Data</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4269,9 +4269,9 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>HR Integration</t>
+          <t>JML Event Log</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>System Logs</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Audit Team</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -4363,14 +4363,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4382,27 +4382,27 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>Role Catalogue</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S4 Assessment Workbook</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4429,27 +4429,27 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.15</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Role Catalogue</t>
+          <t>Procedure Guide</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Process Document</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>S4 Assessment Workbook</t>
+          <t>ISMS Evidence Library</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -4486,17 +4486,17 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>Access Matrix</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Spreadsheet</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S2 Assessment Workbook</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -4504,14 +4504,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Attestation Records</t>
+          <t>Privileged Access List</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Approval Records</t>
+          <t>Access Report</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>S3 Assessment Workbook</t>
+          <t>S2 Assessment Workbook</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Audit Team</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4575,17 +4575,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.15</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Orphaned Scan</t>
+          <t>User Inventory</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Scan Results</t>
+          <t>Spreadsheet</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -4598,9 +4598,9 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -4617,27 +4617,27 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>IAM Policy</t>
+          <t>Orphaned Scan</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Policy Document</t>
+          <t>Scan Results</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>ISMS Evidence Library</t>
+          <t>S1 Assessment Workbook</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>Audit Team</t>
         </is>
       </c>
     </row>
@@ -4664,27 +4664,27 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>Role Catalogue</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S4 Assessment Workbook</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -4711,27 +4711,27 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>A.5.15</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Group Memberships</t>
+          <t>Attestation Records</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Export Data</t>
+          <t>Approval Records</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>S2 Assessment Workbook</t>
+          <t>S3 Assessment Workbook</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -4739,14 +4739,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Audit Team</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -4768,17 +4768,17 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>JML Event Log</t>
+          <t>Attestation Records</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>Approval Records</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>S5 Assessment Workbook</t>
+          <t>S3 Assessment Workbook</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IAM Manager</t>
         </is>
       </c>
     </row>
@@ -4805,27 +4805,27 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>A.5.18</t>
+          <t>A.5.15</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SoD Matrix</t>
+          <t>Orphaned Scan</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Spreadsheet</t>
+          <t>Scan Results</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>S4 Assessment Workbook</t>
+          <t>S1 Assessment Workbook</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -4833,14 +4833,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>CISO</t>
         </is>
       </c>
     </row>
@@ -4880,14 +4880,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -4909,17 +4909,17 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Procedure Guide</t>
+          <t>Attestation Records</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Process Document</t>
+          <t>Approval Records</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>ISMS Evidence Library</t>
+          <t>S3 Assessment Workbook</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -4927,9 +4927,9 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -4946,27 +4946,27 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Procedure Guide</t>
+          <t>JML Event Log</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Process Document</t>
+          <t>System Logs</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>ISMS Evidence Library</t>
+          <t>S5 Assessment Workbook</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>IAM Manager</t>
         </is>
       </c>
     </row>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Access Matrix</t>
+          <t>Privileged Access List</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Spreadsheet</t>
+          <t>Access Report</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -5021,14 +5021,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>CISO</t>
+          <t>IAM Manager</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>IAM Policy</t>
+          <t>Orphaned Scan</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Policy Document</t>
+          <t>Scan Results</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>ISMS Evidence Library</t>
+          <t>S1 Assessment Workbook</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -5068,14 +5068,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>Audit Team</t>
         </is>
       </c>
     </row>
@@ -5087,17 +5087,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>A.5.16</t>
+          <t>A.5.18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>User Inventory</t>
+          <t>Access Matrix</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>S1 Assessment Workbook</t>
+          <t>S2 Assessment Workbook</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>IAM Manager</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -5134,27 +5134,27 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>A.5.18</t>
+          <t>A.5.16</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Orphaned Scan</t>
+          <t>JML Event Log</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Scan Results</t>
+          <t>System Logs</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>S1 Assessment Workbook</t>
+          <t>S5 Assessment Workbook</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -5162,14 +5162,14 @@
           <t>08.02.2026</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Access Matrix</t>
+          <t>Role Catalogue</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Spreadsheet</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>S2 Assessment Workbook</t>
+          <t>S4 Assessment Workbook</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -5349,32 +5349,32 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -5386,32 +5386,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>78.4%</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
           <t>78.3%</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>84.3%</t>
-        </is>
-      </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -5423,32 +5423,32 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
     </row>
@@ -5460,32 +5460,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -5497,32 +5497,32 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+5.3%</t>
         </is>
       </c>
     </row>
@@ -5776,9 +5776,9 @@
           <t>Overall Readiness:</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Mostly Ready</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
     </row>
